--- a/assets/constructions/examples/ctd_mib_chamf.xlsx
+++ b/assets/constructions/examples/ctd_mib_chamf.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,68 +584,88 @@
           <t>dcsfms</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12292511600</t>
+          <t>R215.64-36V50-6012</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M25</t>
+          <t>U-MaxⓇ chamfer milling cutter</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79.7</v>
+        <v>47.78</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>36.5</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>8855</v>
+      </c>
       <c r="L2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>0.84</v>
       </c>
       <c r="N2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SP..1204..</t>
+          <t>Mill 215.64 -SPMT 120408-WL</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx022</t>
+          <t>COR_VARILOCK:50</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>WIDIA_SP1204H</t>
+          <t>COR_R215.64-SP1204H</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -665,17 +685,13 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>WID_SP1204_H</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>WID_SP1204_X2</t>
-        </is>
-      </c>
+          <t>SAND_SP1204_H</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2019 /Novo</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
@@ -683,6 +699,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,7 +714,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R215.64-36V50-6012</t>
+          <t>R215.64-32V50-4512</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -701,10 +723,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47.78</v>
+        <v>48.2</v>
       </c>
       <c r="E3" t="n">
-        <v>36.5</v>
+        <v>32.5</v>
       </c>
       <c r="F3" t="n">
         <v>50</v>
@@ -720,16 +742,16 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>8855</v>
+        <v>9385</v>
       </c>
       <c r="L3" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="M3" t="n">
-        <v>0.84</v>
+        <v>0.738</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -778,68 +800,74 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R215.64-12A20-6012</t>
+          <t>12292511400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>U-MaxⓇ chamfer milling cutter</t>
+          <t>M25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.93</v>
+        <v>66.7</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>25200</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.58</v>
+        <v>0.9</v>
       </c>
       <c r="N4" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mill 215.64 -SPMT 120408-WL</t>
+          <t>SP..1204..</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>COR_R215.64-SP1204H</t>
+          <t>WIDIA_SP1204H</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -859,13 +887,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>SAND_SP1204_H</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>WID_SP1204_H</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>WID_SP1204_X1</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
+          <t>2019 /Novo</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
@@ -873,6 +905,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -882,7 +920,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12292511200</t>
+          <t>12292511600</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -891,10 +929,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.3</v>
+        <v>79.7</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
         <v>22</v>
@@ -903,10 +941,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -914,17 +952,17 @@
         <v>45</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SD..0903..</t>
+          <t>SP..1204..</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -934,7 +972,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>WIDIA_SD0903H</t>
+          <t>WIDIA_SP1204H</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -954,12 +992,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>WID_SD0903_H</t>
+          <t>WID_SP1204_H</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>WID_SD0903_Y1</t>
+          <t>WID_SP1204_X2</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -972,6 +1010,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -981,7 +1025,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R215.64-32V50-4512</t>
+          <t>R215.64-36A32-6012</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -990,16 +1034,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.2</v>
+        <v>47.78</v>
       </c>
       <c r="E6" t="n">
-        <v>32.5</v>
+        <v>36.5</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1009,16 +1053,16 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>9385</v>
+        <v>8855</v>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="M6" t="n">
-        <v>0.738</v>
+        <v>1.115</v>
       </c>
       <c r="N6" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1028,7 +1072,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>COR_VARILOCK:50</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1067,6 +1111,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
